--- a/data/trans_dic/P36BPD07_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P36BPD07_R-Clase-trans_dic.xlsx
@@ -599,7 +599,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>79,79%</t>
+          <t>79,03%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -609,7 +609,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>84,91%</t>
+          <t>83,97%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -619,7 +619,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>82,19%</t>
+          <t>81,35%</t>
         </is>
       </c>
     </row>
@@ -632,32 +632,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>87,16; 93,09</t>
+          <t>87,23; 92,98</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>75,78; 82,99</t>
+          <t>75,48; 82,38</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>85,31; 92,05</t>
+          <t>86,01; 92,38</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>81,97; 87,72</t>
+          <t>80,75; 86,84</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>87,62; 91,86</t>
+          <t>87,65; 91,93</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>79,69; 84,23</t>
+          <t>78,68; 83,55</t>
         </is>
       </c>
     </row>
@@ -679,7 +679,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>74,79%</t>
+          <t>74,32%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -689,7 +689,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>79,29%</t>
+          <t>78,77%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>76,86%</t>
+          <t>76,4%</t>
         </is>
       </c>
     </row>
@@ -712,32 +712,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>84,41; 90,85</t>
+          <t>83,91; 91,12</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>70,5; 78,78</t>
+          <t>70,23; 78,18</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>82,36; 89,69</t>
+          <t>82,21; 89,26</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>75,35; 82,8</t>
+          <t>74,64; 81,99</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>84,42; 89,5</t>
+          <t>84,46; 89,3</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>73,76; 79,49</t>
+          <t>73,42; 79,34</t>
         </is>
       </c>
     </row>
@@ -759,7 +759,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>81,38%</t>
+          <t>70,35%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>77,83%</t>
+          <t>77,42%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -779,7 +779,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>80,67%</t>
+          <t>72,36%</t>
         </is>
       </c>
     </row>
@@ -792,32 +792,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>82,69; 88,87</t>
+          <t>82,01; 88,67</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>68,85; 92,95</t>
+          <t>66,0; 74,66</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>80,34; 91,25</t>
+          <t>80,46; 91,6</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>72,99; 82,84</t>
+          <t>71,59; 81,87</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>83,03; 88,71</t>
+          <t>82,89; 88,47</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>71,89; 91,76</t>
+          <t>68,99; 76,0</t>
         </is>
       </c>
     </row>
@@ -839,7 +839,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>70,19%</t>
+          <t>70,63%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>81,25%</t>
+          <t>75,64%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>75,56%</t>
+          <t>72,79%</t>
         </is>
       </c>
     </row>
@@ -872,32 +872,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>82,83; 87,2</t>
+          <t>82,53; 87,04</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>66,96; 74,02</t>
+          <t>67,68; 73,69</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>80,67; 86,06</t>
+          <t>80,84; 85,93</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>75,23; 91,03</t>
+          <t>72,87; 78,29</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>82,57; 85,9</t>
+          <t>82,62; 85,93</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>71,78; 82,97</t>
+          <t>70,72; 74,68</t>
         </is>
       </c>
     </row>
@@ -919,7 +919,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>65,51%</t>
+          <t>65,78%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -929,7 +929,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>78,4%</t>
+          <t>74,99%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -939,7 +939,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>73,76%</t>
+          <t>71,26%</t>
         </is>
       </c>
     </row>
@@ -952,39 +952,39 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>81,02; 87,21</t>
+          <t>80,78; 86,88</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>60,36; 70,29</t>
+          <t>61,5; 69,93</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>84,36; 89,22</t>
+          <t>84,61; 89,51</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>74,72; 84,21</t>
+          <t>72,42; 77,57</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>83,65; 87,44</t>
+          <t>83,57; 87,44</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>70,47; 78,52</t>
+          <t>68,94; 73,57</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -999,7 +999,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>71,12%</t>
+          <t>66,85%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1009,7 +1009,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>73,16%</t>
+          <t>72,23%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>72,67%</t>
+          <t>71,05%</t>
         </is>
       </c>
     </row>
@@ -1032,32 +1032,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>60,0; 71,59</t>
+          <t>60,31; 72,06</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>61,03; 80,51</t>
+          <t>57,13; 75,47</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>86,14; 90,05</t>
+          <t>86,13; 90,14</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>69,85; 76,28</t>
+          <t>69,17; 75,23</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>81,65; 85,7</t>
+          <t>81,54; 85,63</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>69,35; 75,79</t>
+          <t>67,51; 73,95</t>
         </is>
       </c>
     </row>
@@ -1079,7 +1079,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>73,87%</t>
+          <t>71,4%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>78,94%</t>
+          <t>76,27%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>76,48%</t>
+          <t>73,9%</t>
         </is>
       </c>
     </row>
@@ -1112,32 +1112,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>83,07; 85,57</t>
+          <t>82,97; 85,59</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>71,21; 80,74</t>
+          <t>69,77; 73,09</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>85,52; 87,78</t>
+          <t>85,39; 87,76</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>76,98; 82,77</t>
+          <t>75,03; 77,58</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>84,76; 86,45</t>
+          <t>84,7; 86,44</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>74,67; 79,94</t>
+          <t>72,87; 74,95</t>
         </is>
       </c>
     </row>
@@ -1311,7 +1311,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>403088</t>
+          <t>435141</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -1321,7 +1321,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>378190</t>
+          <t>408380</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1331,7 +1331,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>781277</t>
+          <t>843520</t>
         </is>
       </c>
     </row>
@@ -1344,32 +1344,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>370373; 395608</t>
+          <t>370697; 395131</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>382858; 419255</t>
+          <t>415589; 453618</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>295008; 318307</t>
+          <t>297440; 319475</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>365084; 390686</t>
+          <t>392709; 422326</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>675339; 708019</t>
+          <t>675551; 708594</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>757536; 800685</t>
+          <t>815849; 866359</t>
         </is>
       </c>
     </row>
@@ -1429,7 +1429,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>338218</t>
+          <t>359113</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>303363</t>
+          <t>333315</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1449,7 +1449,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>641580</t>
+          <t>692427</t>
         </is>
       </c>
     </row>
@@ -1462,32 +1462,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>316737; 340927</t>
+          <t>314876; 341928</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>318803; 356233</t>
+          <t>339359; 377795</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>305706; 332906</t>
+          <t>305120; 331289</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>288262; 316764</t>
+          <t>315847; 346955</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>630146; 668030</t>
+          <t>630388; 666515</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>615763; 663584</t>
+          <t>665457; 719075</t>
         </is>
       </c>
     </row>
@@ -1547,7 +1547,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>543151</t>
+          <t>331154</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1557,7 +1557,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>129903</t>
+          <t>145166</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>673053</t>
+          <t>476320</t>
         </is>
       </c>
     </row>
@@ -1580,32 +1580,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>426117; 458001</t>
+          <t>422633; 456940</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>459495; 620370</t>
+          <t>310704; 351471</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>133467; 151588</t>
+          <t>133662; 152177</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>121836; 138277</t>
+          <t>134230; 153511</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>565822; 604527</t>
+          <t>564883; 602916</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>599778; 765560</t>
+          <t>454133; 500248</t>
         </is>
       </c>
     </row>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>725683</t>
+          <t>798637</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1675,7 +1675,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>793548</t>
+          <t>649915</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1685,7 +1685,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1519231</t>
+          <t>1448552</t>
         </is>
       </c>
     </row>
@@ -1698,32 +1698,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>948976; 999131</t>
+          <t>945615; 997252</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>692259; 765254</t>
+          <t>765324; 833317</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>664518; 708923</t>
+          <t>665923; 707827</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>734778; 889078</t>
+          <t>626133; 672696</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1626153; 1691739</t>
+          <t>1627262; 1692343</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1443175; 1668235</t>
+          <t>1407295; 1486057</t>
         </is>
       </c>
     </row>
@@ -1783,7 +1783,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>309909</t>
+          <t>372266</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1793,7 +1793,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>659484</t>
+          <t>622533</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1803,7 +1803,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>969394</t>
+          <t>994799</t>
         </is>
       </c>
     </row>
@@ -1816,39 +1816,39 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>499260; 537383</t>
+          <t>497757; 535327</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>285535; 332506</t>
+          <t>348063; 395755</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>619891; 655667</t>
+          <t>621754; 657802</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>628500; 708339</t>
+          <t>601130; 643891</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>1130172; 1181340</t>
+          <t>1129110; 1181368</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>926137; 1031910</t>
+          <t>962427; 1027085</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1901,7 +1901,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>170262</t>
+          <t>157778</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1911,7 +1911,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>556600</t>
+          <t>609387</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>726862</t>
+          <t>767165</t>
         </is>
       </c>
     </row>
@@ -1934,32 +1934,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>170981; 204012</t>
+          <t>171865; 205358</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>146124; 192750</t>
+          <t>134846; 178129</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>919661; 961372</t>
+          <t>919518; 962334</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>531398; 580378</t>
+          <t>583595; 634659</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1104365; 1159147</t>
+          <t>1102918; 1158288</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>693692; 758091</t>
+          <t>728939; 798439</t>
         </is>
       </c>
     </row>
@@ -2019,7 +2019,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>2490311</t>
+          <t>2454087</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -2029,7 +2029,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2821088</t>
+          <t>2768697</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>5311398</t>
+          <t>5222784</t>
         </is>
       </c>
     </row>
@@ -2052,32 +2052,32 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>2793139; 2877400</t>
+          <t>2789882; 2877959</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>2400659; 2721840</t>
+          <t>2398262; 2512188</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3001065; 3080602</t>
+          <t>2996685; 3079887</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2750875; 2957921</t>
+          <t>2723676; 2815983</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>5824636; 5940332</t>
+          <t>5820729; 5940220</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>5185839; 5551346</t>
+          <t>5149587; 5296804</t>
         </is>
       </c>
     </row>
